--- a/AIWine Wine Upload Template.xlsx
+++ b/AIWine Wine Upload Template.xlsx
@@ -59,7 +59,6 @@
     <col min="11" max="11" width="42" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -128,11 +127,6 @@
           <t xml:space="preserve">Awards (semicolon ;)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Off-licence number</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -194,11 +188,6 @@
           <t xml:space="preserve">Gold · NZ IWS 2025</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12/OFF/0356/2024</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -253,11 +242,6 @@
       <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">oysters; goat cheese; thai salad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12/OFF/0356/2024</t>
         </is>
       </c>
     </row>
@@ -347,42 +331,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Off-licence number (required for compliance)</t>
+          <t xml:space="preserve">Selling &amp; licensing</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Enter your winery’s off-licence number (e.g. 12/OFF/0356/2024).</t>
+          <t xml:space="preserve">• AIWine Ventures Limited is the licensed seller of alcohol (Sale and Supply of Alcohol Act 2012).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">• It is the SAME on every row — it is your winery’s licence, not the wine’s.</t>
+          <t xml:space="preserve">• You list and price your wines and dispatch orders; AIWine handles the sale and compliance.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">• It appears on every wine listing as “Sold &amp; supplied by [your winery] · Off-Licence No. …”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• A copy of your certificate is captured separately in the portal and shown on your cellar-door page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• You sell as the licensed winery; AIWine is your sales agent under the Sale and Supply of Alcohol Act 2012.</t>
+          <t xml:space="preserve">• No licence details are needed from you on this sheet.</t>
         </is>
       </c>
     </row>

--- a/AIWine Wine Upload Template.xlsx
+++ b/AIWine Wine Upload Template.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Your wines" sheetId="1" r:id="rId1"/>
-    <sheet name="Read me" sheetId="2" r:id="rId2"/>
+    <sheet name="Wines" sheetId="1" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
+    <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -20,13 +21,25 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF888888"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -35,36 +48,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="42" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wine name</t>
+          <t xml:space="preserve">Wine Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -74,7 +87,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colour</t>
+          <t xml:space="preserve">Colour / Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -89,175 +102,247 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stock</t>
+          <t xml:space="preserve">Stock (bottles)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tasting Notes (max 25 words)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Food Pairings (max 3; semicolon ;)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Style</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Organic (Y/N)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Awards (semicolon ;)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sub-region</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tasting notes (max 25 words)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Food pairings (semicolon ;)</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Awards (semicolon ;)</t>
+          <t xml:space="preserve">Sub-Region</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crimson Pinot Noir</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXAMPLE — delete this row</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Pinot Noir</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Red</t>
         </is>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>2023</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>32</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>60</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perfumed and bright — cherry, plum and soft spice from younger vines.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roast duck; salmon; mushroom risotto</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">medium-bodied</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gold · NZ IWS 2025</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wairarapa</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martinborough</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXAMPLE — delete this row</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chardonnay</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>2023</v>
+      </c>
+      <c r="E3" s="2">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2">
+        <v>40</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Citrus and white peach with a flinty, savoury finish.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roast chicken; creamy pasta</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">medium-bodied</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Wairarapa</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Martinborough</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bright cherry, plum and soft spice — an easy, food-friendly red.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">roast duck; mushroom risotto; pizza</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gold · NZ IWS 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Te Wā Sauvignon Blanc</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sauvignon Blanc</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">White</t>
-        </is>
-      </c>
-      <c r="D3">
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXAMPLE — delete this row</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rosé</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rosé</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
         <v>2024</v>
       </c>
-      <c r="E3">
-        <v>38</v>
-      </c>
-      <c r="F3">
-        <v>28</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E4" s="2">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pale, dry and Provençal — strawberry and citrus.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">salads; aperitif; charcuterie</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">light</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Wairarapa</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martinborough</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Citrus, fresh-cut grass and a crisp, zesty finish.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oysters; goat cheese; thai salad</t>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gladstone</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C400">
-      <formula1>"Red,White,Rosé,Sparkling,Dessert,Fortified"</formula1>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B200">
+      <formula1>Lists!$A$2:$A$23</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G400">
-      <formula1>"light,medium-bodied,full-bodied"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C200">
+      <formula1>Lists!$B$2:$B$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H400">
-      <formula1>"Y,N"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I200">
+      <formula1>Lists!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I400">
-      <formula1>"Northland,Auckland,Waikato &amp; Bay of Plenty,Gisborne,Hawke’s Bay,Wairarapa,Nelson,Marlborough,North Canterbury,Waitaki Valley,Central Otago,Other"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J200">
+      <formula1>Lists!$E$2:$E$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L200">
+      <formula1>Lists!$C$2:$C$13</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M200">
+      <formula1>Lists!$D$2:$D$17</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -266,7 +351,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
+    <col min="1" max="1" width="96" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -276,83 +361,854 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Delete the three grey EXAMPLE rows on the Wines tab (they are skipped on import anyway).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Add one row per wine. Use the dropdowns for Variety, Colour/Type, Style, Organic, Region and Sub-Region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Save as .xlsx or .csv and upload in the AIWine portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tasting Notes — keep to about 25 words (≈160 characters). Longer notes are shortened on import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Food Pairings — up to 3, separated by a semicolon ;  (only the first 3 are shown).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Awards — separated by a semicolon ;  Leave blank if none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colour / Type — Red, White, Rosé, Sparkling, Dessert or Fortified. Drives the website variety filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organic — Y or N.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Price — bottle price including GST.   Stock — bottles available (0 = sold out).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anything left blank is fine — you can fill it in later in the portal.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="6" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variety</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colour</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sub-Region</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organic</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Style</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sparkling</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Northland</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">light</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill in one row per wine on the “Your wines” tab, then upload it in the AIWine portal (Upload list).</t>
+          <t xml:space="preserve">Sauvignon Blanc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auckland</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martinborough</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">medium-bodied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete the two grey example rows before you upload — they are skipped automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+          <t xml:space="preserve">Riesling</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rosé</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waikato &amp; Bay of Plenty</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gladstone</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">full-bodied</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pinot Gris</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sparkling</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gisborne</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masterton</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columns</t>
+          <t xml:space="preserve">Gewürztraminer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dessert</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hawke’s Bay</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiheke Island</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Wine name, Variety, Colour, Vintage, Price (incl GST), Stock — the essentials.</t>
+          <t xml:space="preserve">Albariño</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fortified</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wairarapa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matakana</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Style / Organic / Region — use the dropdowns so spelling stays consistent.</t>
+          <t xml:space="preserve">Viognier</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nelson</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gimblett Gravels</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Tasting notes — kept to about 25 words so wine cards stay tidy.</t>
+          <t xml:space="preserve">Chardonnay</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marlborough</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bridge Pa</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Food pairings &amp; Awards — separate multiple entries with a semicolon ;</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t xml:space="preserve">Chenin Blanc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North Canterbury</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bannockburn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semillon</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waitaki Valley</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gibbston</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selling &amp; licensing</t>
+          <t xml:space="preserve">White Blend</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central Otago</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bendigo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">• AIWine Ventures Limited is the licensed seller of alcohol (Sale and Supply of Alcohol Act 2012).</t>
+          <t xml:space="preserve">Rosé</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lowburn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">• You list and price your wines and dispatch orders; AIWine handles the sale and compliance.</t>
+          <t xml:space="preserve">Pinot Noir</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Awatere Valley</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">• No licence details are needed from you on this sheet.</t>
+          <t xml:space="preserve">Syrah</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wairau Valley</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merlot</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southern Valleys</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cabernet Sauvignon</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waipara</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malbec</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tempranillo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Blend</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dessert</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fortified</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>

--- a/AIWine Wine Upload Template.xlsx
+++ b/AIWine Wine Upload Template.xlsx
@@ -72,6 +72,7 @@
     <col min="11" max="11" width="26" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -140,6 +141,11 @@
           <t xml:space="preserve">Sub-Region</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Image File Name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -201,6 +207,11 @@
           <t xml:space="preserve">Martinborough</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chimney-pinot-noir-2023.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -262,6 +273,11 @@
           <t xml:space="preserve">Martinborough</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homestead-chardonnay-2024.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -323,6 +339,491 @@
           <t xml:space="preserve">Gladstone</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">river-paddock-rose-2024.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0"/>
+      <c r="B5" s="0"/>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="J5" s="0"/>
+      <c r="K5" s="0"/>
+      <c r="L5" s="0"/>
+      <c r="M5" s="0"/>
+      <c r="N5" s="0"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="0"/>
+      <c r="B6" s="0"/>
+      <c r="C6" s="0"/>
+      <c r="D6" s="0"/>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
+      <c r="L6" s="0"/>
+      <c r="M6" s="0"/>
+      <c r="N6" s="0"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0"/>
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
+      <c r="M7" s="0"/>
+      <c r="N7" s="0"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0"/>
+      <c r="B8" s="0"/>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="0"/>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
+      <c r="I8" s="0"/>
+      <c r="J8" s="0"/>
+      <c r="K8" s="0"/>
+      <c r="L8" s="0"/>
+      <c r="M8" s="0"/>
+      <c r="N8" s="0"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0"/>
+      <c r="J9" s="0"/>
+      <c r="K9" s="0"/>
+      <c r="L9" s="0"/>
+      <c r="M9" s="0"/>
+      <c r="N9" s="0"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="0"/>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+      <c r="D10" s="0"/>
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+      <c r="I10" s="0"/>
+      <c r="J10" s="0"/>
+      <c r="K10" s="0"/>
+      <c r="L10" s="0"/>
+      <c r="M10" s="0"/>
+      <c r="N10" s="0"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="0"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0"/>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="J11" s="0"/>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
+      <c r="N11" s="0"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
+      <c r="N12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="0"/>
+      <c r="L13" s="0"/>
+      <c r="M13" s="0"/>
+      <c r="N13" s="0"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+      <c r="I14" s="0"/>
+      <c r="J14" s="0"/>
+      <c r="K14" s="0"/>
+      <c r="L14" s="0"/>
+      <c r="M14" s="0"/>
+      <c r="N14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="0"/>
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+      <c r="D15" s="0"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+      <c r="I15" s="0"/>
+      <c r="J15" s="0"/>
+      <c r="K15" s="0"/>
+      <c r="L15" s="0"/>
+      <c r="M15" s="0"/>
+      <c r="N15" s="0"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
+      <c r="L16" s="0"/>
+      <c r="M16" s="0"/>
+      <c r="N16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
+      <c r="I17" s="0"/>
+      <c r="J17" s="0"/>
+      <c r="K17" s="0"/>
+      <c r="L17" s="0"/>
+      <c r="M17" s="0"/>
+      <c r="N17" s="0"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0"/>
+      <c r="B18" s="0"/>
+      <c r="C18" s="0"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+      <c r="I18" s="0"/>
+      <c r="J18" s="0"/>
+      <c r="K18" s="0"/>
+      <c r="L18" s="0"/>
+      <c r="M18" s="0"/>
+      <c r="N18" s="0"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+      <c r="C19" s="0"/>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+      <c r="I19" s="0"/>
+      <c r="J19" s="0"/>
+      <c r="K19" s="0"/>
+      <c r="L19" s="0"/>
+      <c r="M19" s="0"/>
+      <c r="N19" s="0"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="0"/>
+      <c r="B20" s="0"/>
+      <c r="C20" s="0"/>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0"/>
+      <c r="H20" s="0"/>
+      <c r="I20" s="0"/>
+      <c r="J20" s="0"/>
+      <c r="K20" s="0"/>
+      <c r="L20" s="0"/>
+      <c r="M20" s="0"/>
+      <c r="N20" s="0"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+      <c r="C21" s="0"/>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0"/>
+      <c r="G21" s="0"/>
+      <c r="H21" s="0"/>
+      <c r="I21" s="0"/>
+      <c r="J21" s="0"/>
+      <c r="K21" s="0"/>
+      <c r="L21" s="0"/>
+      <c r="M21" s="0"/>
+      <c r="N21" s="0"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="0"/>
+      <c r="B22" s="0"/>
+      <c r="C22" s="0"/>
+      <c r="D22" s="0"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0"/>
+      <c r="G22" s="0"/>
+      <c r="H22" s="0"/>
+      <c r="I22" s="0"/>
+      <c r="J22" s="0"/>
+      <c r="K22" s="0"/>
+      <c r="L22" s="0"/>
+      <c r="M22" s="0"/>
+      <c r="N22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0"/>
+      <c r="B23" s="0"/>
+      <c r="C23" s="0"/>
+      <c r="D23" s="0"/>
+      <c r="E23" s="0"/>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
+      <c r="I23" s="0"/>
+      <c r="J23" s="0"/>
+      <c r="K23" s="0"/>
+      <c r="L23" s="0"/>
+      <c r="M23" s="0"/>
+      <c r="N23" s="0"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="0"/>
+      <c r="B24" s="0"/>
+      <c r="C24" s="0"/>
+      <c r="D24" s="0"/>
+      <c r="E24" s="0"/>
+      <c r="F24" s="0"/>
+      <c r="G24" s="0"/>
+      <c r="H24" s="0"/>
+      <c r="I24" s="0"/>
+      <c r="J24" s="0"/>
+      <c r="K24" s="0"/>
+      <c r="L24" s="0"/>
+      <c r="M24" s="0"/>
+      <c r="N24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
+      <c r="C25" s="0"/>
+      <c r="D25" s="0"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+      <c r="I25" s="0"/>
+      <c r="J25" s="0"/>
+      <c r="K25" s="0"/>
+      <c r="L25" s="0"/>
+      <c r="M25" s="0"/>
+      <c r="N25" s="0"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="0"/>
+      <c r="B26" s="0"/>
+      <c r="C26" s="0"/>
+      <c r="D26" s="0"/>
+      <c r="E26" s="0"/>
+      <c r="F26" s="0"/>
+      <c r="G26" s="0"/>
+      <c r="H26" s="0"/>
+      <c r="I26" s="0"/>
+      <c r="J26" s="0"/>
+      <c r="K26" s="0"/>
+      <c r="L26" s="0"/>
+      <c r="M26" s="0"/>
+      <c r="N26" s="0"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="0"/>
+      <c r="B27" s="0"/>
+      <c r="C27" s="0"/>
+      <c r="D27" s="0"/>
+      <c r="E27" s="0"/>
+      <c r="F27" s="0"/>
+      <c r="G27" s="0"/>
+      <c r="H27" s="0"/>
+      <c r="I27" s="0"/>
+      <c r="J27" s="0"/>
+      <c r="K27" s="0"/>
+      <c r="L27" s="0"/>
+      <c r="M27" s="0"/>
+      <c r="N27" s="0"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+      <c r="C28" s="0"/>
+      <c r="D28" s="0"/>
+      <c r="E28" s="0"/>
+      <c r="F28" s="0"/>
+      <c r="G28" s="0"/>
+      <c r="H28" s="0"/>
+      <c r="I28" s="0"/>
+      <c r="J28" s="0"/>
+      <c r="K28" s="0"/>
+      <c r="L28" s="0"/>
+      <c r="M28" s="0"/>
+      <c r="N28" s="0"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="0"/>
+      <c r="B29" s="0"/>
+      <c r="C29" s="0"/>
+      <c r="D29" s="0"/>
+      <c r="E29" s="0"/>
+      <c r="F29" s="0"/>
+      <c r="G29" s="0"/>
+      <c r="H29" s="0"/>
+      <c r="I29" s="0"/>
+      <c r="J29" s="0"/>
+      <c r="K29" s="0"/>
+      <c r="L29" s="0"/>
+      <c r="M29" s="0"/>
+      <c r="N29" s="0"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="0"/>
+      <c r="B30" s="0"/>
+      <c r="C30" s="0"/>
+      <c r="D30" s="0"/>
+      <c r="E30" s="0"/>
+      <c r="F30" s="0"/>
+      <c r="G30" s="0"/>
+      <c r="H30" s="0"/>
+      <c r="I30" s="0"/>
+      <c r="J30" s="0"/>
+      <c r="K30" s="0"/>
+      <c r="L30" s="0"/>
+      <c r="M30" s="0"/>
+      <c r="N30" s="0"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0"/>
+      <c r="B31" s="0"/>
+      <c r="C31" s="0"/>
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
+      <c r="F31" s="0"/>
+      <c r="G31" s="0"/>
+      <c r="H31" s="0"/>
+      <c r="I31" s="0"/>
+      <c r="J31" s="0"/>
+      <c r="K31" s="0"/>
+      <c r="L31" s="0"/>
+      <c r="M31" s="0"/>
+      <c r="N31" s="0"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="0"/>
+      <c r="B32" s="0"/>
+      <c r="C32" s="0"/>
+      <c r="D32" s="0"/>
+      <c r="E32" s="0"/>
+      <c r="F32" s="0"/>
+      <c r="G32" s="0"/>
+      <c r="H32" s="0"/>
+      <c r="I32" s="0"/>
+      <c r="J32" s="0"/>
+      <c r="K32" s="0"/>
+      <c r="L32" s="0"/>
+      <c r="M32" s="0"/>
+      <c r="N32" s="0"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="0"/>
+      <c r="B33" s="0"/>
+      <c r="C33" s="0"/>
+      <c r="D33" s="0"/>
+      <c r="E33" s="0"/>
+      <c r="F33" s="0"/>
+      <c r="G33" s="0"/>
+      <c r="H33" s="0"/>
+      <c r="I33" s="0"/>
+      <c r="J33" s="0"/>
+      <c r="K33" s="0"/>
+      <c r="L33" s="0"/>
+      <c r="M33" s="0"/>
+      <c r="N33" s="0"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+      <c r="C34" s="0"/>
+      <c r="D34" s="0"/>
+      <c r="E34" s="0"/>
+      <c r="F34" s="0"/>
+      <c r="G34" s="0"/>
+      <c r="H34" s="0"/>
+      <c r="I34" s="0"/>
+      <c r="J34" s="0"/>
+      <c r="K34" s="0"/>
+      <c r="L34" s="0"/>
+      <c r="M34" s="0"/>
+      <c r="N34" s="0"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -466,6 +967,69 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bottle images — how matching works (please read)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every wine can have one bottle photo. We match each photo to a wine BY ITS FILE NAME, so the name must be exact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Fill in the Image File Name column on the Wines tab for each wine, e.g.  chimney-pinot-noir-2023.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Name the photo file on your computer EXACTLY the same (case doesn’t matter, spaces vs dashes don’t matter).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Upload the photos on the portal’s Wine Images page (drag them all in at once) — each lands on the right wine automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tip: the safest file name is the wine name plus vintage:  Wine Name + vintage  →  homestead-chardonnay-2024.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If a file name doesn’t match any wine, we’ll show it as “unmatched” and let you assign it with one click — nothing is lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JPG or PNG, up to 10 MB. Photos are resized automatically — a phone photo in daylight is perfect.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/AIWine Wine Upload Template.xlsx
+++ b/AIWine Wine Upload Template.xlsx
@@ -49,7 +49,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -826,6 +828,7 @@
       <c r="N34" s="0"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="1" insertColumns="0" deleteRows="1" deleteColumns="0" sort="1" autoFilter="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B200">
       <formula1>Lists!$A$2:$A$23</formula1>

--- a/AIWine Wine Upload Template.xlsx
+++ b/AIWine Wine Upload Template.xlsx
@@ -49,9 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -828,7 +826,6 @@
       <c r="N34" s="0"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="1" insertColumns="0" deleteRows="1" deleteColumns="0" sort="1" autoFilter="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B200">
       <formula1>Lists!$A$2:$A$23</formula1>

--- a/AIWine Wine Upload Template.xlsx
+++ b/AIWine Wine Upload Template.xlsx
@@ -280,70 +280,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EXAMPLE — delete this row</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rosé</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rosé</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>2024</v>
-      </c>
-      <c r="E4" s="2">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2">
-        <v>36</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pale, dry and Provençal — strawberry and citrus.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">salads; aperitif; charcuterie</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">light</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wairarapa</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gladstone</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">river-paddock-rose-2024.jpg</t>
-        </is>
-      </c>
+      <c r="A4" s="0"/>
+      <c r="B4" s="0"/>
+      <c r="C4" s="0"/>
+      <c r="D4" s="0"/>
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
+      <c r="J4" s="0"/>
+      <c r="K4" s="0"/>
+      <c r="L4" s="0"/>
+      <c r="M4" s="0"/>
+      <c r="N4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0"/>
@@ -879,7 +829,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Delete the three grey EXAMPLE rows on the Wines tab (they are skipped on import anyway).</t>
+          <t xml:space="preserve">1. Delete the two grey EXAMPLE rows on the Wines tab (they are skipped on import anyway).</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1025,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sparkling</t>
+          <t xml:space="preserve">Albariño</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red</t>
+          <t xml:space="preserve">Dessert</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Northland</t>
+          <t xml:space="preserve">Auckland</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1095,66 +1045,66 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">light</t>
+          <t xml:space="preserve">full-bodied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sauvignon Blanc</t>
+          <t xml:space="preserve">Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">White</t>
+          <t xml:space="preserve">Fortified</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auckland</t>
+          <t xml:space="preserve">Central Otago</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martinborough</t>
+          <t xml:space="preserve">Awatere Valley</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium-bodied</t>
+          <t xml:space="preserve">light</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riesling</t>
+          <t xml:space="preserve">Chardonnay</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosé</t>
+          <t xml:space="preserve">Red</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waikato &amp; Bay of Plenty</t>
+          <t xml:space="preserve">Gisborne</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladstone</t>
+          <t xml:space="preserve">Bannockburn</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1164,29 +1114,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">full-bodied</t>
+          <t xml:space="preserve">medium-bodied</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinot Gris</t>
+          <t xml:space="preserve">Chenin Blanc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sparkling</t>
+          <t xml:space="preserve">Rosé</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gisborne</t>
+          <t xml:space="preserve">Hawke’s Bay</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masterton</t>
+          <t xml:space="preserve">Bendigo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1203,22 +1153,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gewürztraminer</t>
+          <t xml:space="preserve">Dessert</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dessert</t>
+          <t xml:space="preserve">Sparkling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hawke’s Bay</t>
+          <t xml:space="preserve">Marlborough</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waiheke Island</t>
+          <t xml:space="preserve">Bridge Pa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1235,22 +1185,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albariño</t>
+          <t xml:space="preserve">Fortified</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortified</t>
+          <t xml:space="preserve">White</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wairarapa</t>
+          <t xml:space="preserve">Nelson</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matakana</t>
+          <t xml:space="preserve">Gibbston</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1267,7 +1217,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viognier</t>
+          <t xml:space="preserve">Gewürztraminer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1277,7 +1227,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nelson</t>
+          <t xml:space="preserve">North Canterbury</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1299,7 +1249,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chardonnay</t>
+          <t xml:space="preserve">Malbec</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1309,12 +1259,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marlborough</t>
+          <t xml:space="preserve">Northland</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bridge Pa</t>
+          <t xml:space="preserve">Gladstone</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1331,7 +1281,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chenin Blanc</t>
+          <t xml:space="preserve">Merlot</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,12 +1291,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">North Canterbury</t>
+          <t xml:space="preserve">Waikato &amp; Bay of Plenty</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bannockburn</t>
+          <t xml:space="preserve">Lowburn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1363,7 +1313,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semillon</t>
+          <t xml:space="preserve">Pinot Gris</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1373,12 +1323,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waitaki Valley</t>
+          <t xml:space="preserve">Wairarapa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gibbston</t>
+          <t xml:space="preserve">Martinborough</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1395,7 +1345,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">White Blend</t>
+          <t xml:space="preserve">Pinot Noir</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1405,12 +1355,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Central Otago</t>
+          <t xml:space="preserve">Waitaki Valley</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bendigo</t>
+          <t xml:space="preserve">Masterton</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1427,7 +1377,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosé</t>
+          <t xml:space="preserve">Red Blend</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1442,7 +1392,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lowburn</t>
+          <t xml:space="preserve">Matakana</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1459,7 +1409,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinot Noir</t>
+          <t xml:space="preserve">Riesling</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1474,7 +1424,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Awatere Valley</t>
+          <t xml:space="preserve">Southern Valleys</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1491,7 +1441,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syrah</t>
+          <t xml:space="preserve">Rosé</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1506,7 +1456,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wairau Valley</t>
+          <t xml:space="preserve">Waiheke Island</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1523,7 +1473,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merlot</t>
+          <t xml:space="preserve">Sauvignon Blanc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1538,7 +1488,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southern Valleys</t>
+          <t xml:space="preserve">Waipara</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1555,7 +1505,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cabernet Sauvignon</t>
+          <t xml:space="preserve">Semillon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1570,7 +1520,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waipara</t>
+          <t xml:space="preserve">Wairau Valley</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1587,7 +1537,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malbec</t>
+          <t xml:space="preserve">Sparkling</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1619,7 +1569,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempranillo</t>
+          <t xml:space="preserve">Syrah</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1651,7 +1601,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red Blend</t>
+          <t xml:space="preserve">Tempranillo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1683,7 +1633,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dessert</t>
+          <t xml:space="preserve">Viognier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1715,7 +1665,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortified</t>
+          <t xml:space="preserve">White Blend</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
